--- a/data/country_maps/spain_review.xlsx
+++ b/data/country_maps/spain_review.xlsx
@@ -2128,7 +2128,7 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>livesp1</t>
+          <t>smharm6</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2868,7 +2868,11 @@
           <t>Cooperation. Over the past six months... | Never true | Sometimes true | Often true | Prefer not to answer | You blame others for your own mistakes. | You are irritable and get angry. | You lose your temper. | You are defiant or uncooperative. | You argue or talk back to adults. | You are resentful or spiteful.</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr"/>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>bcfpi_coop1</t>
+        </is>
+      </c>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="5" t="inlineStr"/>
@@ -2906,7 +2910,11 @@
           <t>Managing anxiety. During the past six months... | Never true | Sometimes true | Often true | Prefer not to answer | You feel anxious or nervous about things in general. | You avoid or delay tasks due to anxiety. | You worry about being better at what you do. | You worry about your past behavior. | You worry about doing something wrong. | You worry about things in the future. | You are afraid of making mistakes.</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr"/>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>bcfpi_ma1</t>
+        </is>
+      </c>
       <c r="H57" s="5" t="inlineStr"/>
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="5" t="inlineStr"/>
@@ -3190,11 +3198,7 @@
           <t>School: My teachers care about me.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>bcfpi_coop1</t>
-        </is>
-      </c>
+      <c r="G63" s="2" t="n"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Please select the response that best reflects how you have felt or behaved over the past six months. You...</t>
@@ -4310,11 +4314,7 @@
           <t>School: We learn many interesting things in school.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>bcfpi_ma1</t>
-        </is>
-      </c>
+      <c r="G93" s="2" t="n"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Please select the response that best reflects how you have felt or behaved over the past six months. You...</t>
@@ -5970,7 +5970,11 @@
           <t>Emotion regulation. During the past six months... | Never true | Sometimes true | Often true | Prefer not to answer | You have trouble controlling your emotions. | You find it very difficult to calm down when you get angry. | You feel like your emotions overwhelm you and you can't do anything about it. | You try hard not to think about your feelings. | You believe it is better to control your emotions and not think about them. | You keep your feelings to yourself.</t>
         </is>
       </c>
-      <c r="G135" s="5" t="inlineStr"/>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>bcfpi_af1</t>
+        </is>
+      </c>
       <c r="H135" s="5" t="inlineStr"/>
       <c r="I135" s="5" t="inlineStr"/>
       <c r="J135" s="5" t="inlineStr"/>
@@ -6254,11 +6258,7 @@
           <t>Relationship with parents Please indicate how often you feel this way in your family.: My parents hurt my feelings.</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>bcfpi_af1</t>
-        </is>
-      </c>
+      <c r="G141" s="2" t="n"/>
       <c r="H141" s="2" t="inlineStr">
         <is>
           <t>Please select the response that best reflects how you have felt or behaved over the past six months. You...</t>
@@ -7334,7 +7334,11 @@
           <t>Relationship with parents/guardians During your life up to now... | Always | Most of the time | Sometimes | Rarely | Never | Prefer not to answer | Did your parents / guardians understand your problems and concerns? | Did your parents / guardians really know what you did in your free time when you were not at school or work?</t>
         </is>
       </c>
-      <c r="G169" s="5" t="inlineStr"/>
+      <c r="G169" s="5" t="inlineStr">
+        <is>
+          <t>rpginsfy1</t>
+        </is>
+      </c>
       <c r="H169" s="5" t="inlineStr"/>
       <c r="I169" s="5" t="inlineStr"/>
       <c r="J169" s="5" t="inlineStr"/>
@@ -8008,7 +8012,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>dlup1</t>
+          <t>rpginsfy2</t>
         </is>
       </c>
       <c r="H183" s="3" t="inlineStr">
@@ -8064,7 +8068,11 @@
           <t>During your life up to now... | Yes | No | Prefer not to answer | Did you live with any family member who had problems with alcohol or was an alcoholic, or who abused illegal or prescription drugs? | Did you live with any family member who was depressed, had a mental illness, or exhibited suicidal behavior? | Did you live with any family member who had been in jail or prison? | Did your parents ever separate or divorce? | Did your mother, father, or guardian pass away?</t>
         </is>
       </c>
-      <c r="G184" s="5" t="inlineStr"/>
+      <c r="G184" s="5" t="inlineStr">
+        <is>
+          <t>dlup1</t>
+        </is>
+      </c>
       <c r="H184" s="5" t="inlineStr"/>
       <c r="I184" s="5" t="inlineStr"/>
       <c r="J184" s="5" t="inlineStr"/>
@@ -9384,7 +9392,11 @@
           <t>To what extent do the following statements apply to you? | Not at all | A little | Somewhat | Quite a bit | A lot | Prefer not to answer | I have people I look up to. | Getting an education is important to me. | My parents / guardians know a lot about me. | I try to finish what I start. | I solve problems without harming myself or others (without resorting to drugs or violence). | I know where to go in my community to get help. | I feel like I belong at my school. | My family supports me in difficult times. | My friends support me in difficult times. | I am treated fairly in my community. | I have opportunities to develop skills that will be useful to me later on. | I enjoy my cultural and family traditions.</t>
         </is>
       </c>
-      <c r="G210" s="5" t="inlineStr"/>
+      <c r="G210" s="5" t="inlineStr">
+        <is>
+          <t>cyrm01</t>
+        </is>
+      </c>
       <c r="H210" s="5" t="inlineStr"/>
       <c r="I210" s="5" t="inlineStr"/>
       <c r="J210" s="5" t="inlineStr"/>
@@ -9568,11 +9580,7 @@
           <t>Relationship with friends To what extent do the following statements apply to you?: I have many friends.</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr">
-        <is>
-          <t>cyrm01</t>
-        </is>
-      </c>
+      <c r="G214" s="2" t="n"/>
       <c r="H214" s="2" t="inlineStr">
         <is>
           <t>To what extent do the following statements apply to you?</t>
@@ -11458,7 +11466,11 @@
           <t>For each of the following areas of your life, indicate how often using your phone, computer, or video game console has a negative effect: | Almost always | Often | Sometimes | Rarely | Never | Prefer not to respond | Sleep. | Schoolwork. | Self-esteem / Mental health. | Relationships with friends. | Relationships with family.</t>
         </is>
       </c>
-      <c r="G251" s="5" t="inlineStr"/>
+      <c r="G251" s="5" t="inlineStr">
+        <is>
+          <t>smharm1</t>
+        </is>
+      </c>
       <c r="H251" s="5" t="inlineStr"/>
       <c r="I251" s="5" t="inlineStr"/>
       <c r="J251" s="5" t="inlineStr"/>
@@ -11492,11 +11504,7 @@
           <t>Select the option that you consider most appropriate for your situation: : I sleep less because I am using my mobile phone.</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr">
-        <is>
-          <t>smharm1</t>
-        </is>
-      </c>
+      <c r="G252" s="2" t="n"/>
       <c r="H252" s="2" t="inlineStr">
         <is>
           <t>For each of the following life areas, please indicate how often your use of phone, computer or gaming console has a negative effect</t>
